--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260819.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260819.xlsx
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>2,318,000</t>
+          <t>3,534,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>3,534,000</t>
+          <t>2,318,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>17,902,000</t>
+          <t>18,940,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>18,940,000</t>
+          <t>17,902,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
